--- a/corpus/xlsx/level-008/template.xlsx
+++ b/corpus/xlsx/level-008/template.xlsx
@@ -68,38 +68,38 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{title}}</t>
+          <t xml:space="preserve">{d.title}</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{count}}</t>
+          <t xml:space="preserve">{d.count}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{spaced}}</t>
+          <t xml:space="preserve">{d.spaced}</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{enabled}}</t>
+          <t xml:space="preserve">{d.enabled}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{literal}}</t>
+          <t xml:space="preserve">{d.literal}</t>
         </is>
       </c>
       <c r="B4" s="0">
@@ -109,56 +109,56 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer}}</t>
+          <t xml:space="preserve">{d.customer}</t>
         </is>
       </c>
     </row>
